--- a/static/marchMadness/2026/ExcelBrackets/alice-march-madness-bracket-2026.xlsx
+++ b/static/marchMadness/2026/ExcelBrackets/alice-march-madness-bracket-2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_7F3B82D9C5135915765D16462BF5BCAF63801E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65648D31-EF91-484E-88FB-1BCFA20822E1}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_7F3B82D9C5135915765D16462BF5BCAF63801E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29D24BFE-D786-4719-8DCD-34B1AE5DB35E}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -301,6 +301,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
